--- a/Final_Amazon_Upload.xlsx
+++ b/Final_Amazon_Upload.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,101 +413,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>item_sku</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>item_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>external_product_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>external_product_id_type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>feed_product_type</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>standard_price</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>update_delete</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>product_description</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>bullet_point1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>bullet_point2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>bullet_point3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>department_name</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>generic_keywords</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>main_image_url</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>other_image_url1</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>other_image_url2</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>other_image_url3</t>
         </is>
@@ -528,7 +516,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SWT-KUR-1766675340-1</t>
+          <t>SWT-KUR-1771586473-1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -538,7 +526,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweet India kurta set for women kurti pant with dupatta</t>
+          <t>Sweet India Aishani Fashionable Tops&amp; Bottom</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -549,7 +537,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>729</v>
+        <v>523</v>
       </c>
       <c r="H2" t="n">
         <v>50</v>
@@ -563,49 +551,59 @@
         <is>
           <t>Name
  : 
-kurta set for women kurti pant with dupatta
-Kurta Fabric
- : 
-Cotton Blend
-Bottomwear Fabric
- : 
-Cotton Blend
+Aishani Fashionable Tops&amp; Bottom
+Top Fabric
+ : 
+Crepe
+Bottom Fabric
+ : 
+Crepe
 Sleeve Length
  : 
-Three-Quarter Sleeves
-Pattern
- : 
-Printed
-Set Type
- : 
-Kurta with Dupatta and Bottomwear
-Stitch Type
- : 
-Stitched
+Short Sleeves
 Net Quantity (N)
  : 
-Single
-Discover exquisite women kurta sets for every occasion kurti pant sets! Explore our curated collection of trendy designs, vibrant colors, and comfortable fabrics. From traditional to contemporary styles, find the perfect kurta set to elevate your ethnic wardrobe. Shop now and embrace timeless elegance with our versatile range of women kurta sets
+1
 Sizes
  : 
-XS (Bust Size
- : 
-34 in, Bottom Waist Size: 28 in, Bottom Length Size: 42 in, Shoulder Size: 14 in)
-S (Bust Size
- : 
-36 in, Bottom Waist Size: 28 in, Bottom Length Size: 42 in, Shoulder Size: 14.5 in)
-M (Bust Size
- : 
-38 in, Bottom Waist Size: 30 in, Bottom Length Size: 42 in, Shoulder Size: 15 in)
-L (Bust Size
- : 
-40 in, Bottom Waist Size: 30 in, Bottom Length Size: 42 in, Shoulder Size: 10.5 in)
-XL (Bust Size
- : 
-42 in, Bottom Waist Size: 32 in, Bottom Length Size: 42 in, Shoulder Size: 16 in)
-XXL (Bust Size
- : 
-44 in, Bottom Waist Size: 32 in, Bottom Length Size: 42 in, Shoulder Size: 16.5 in)
+S (Top Bust Size
+ : 
+36 in, Top Length Size: 14 in, Bottom Waist Size: 28 in, Bottom Length Size: 38 in)
+M (Top Bust Size
+ : 
+38 in, Top Length Size: 14 in, Bottom Waist Size: 30 in, Bottom Length Size: 38 in)
+L (Top Bust Size
+ : 
+40 in, Top Length Size: 14 in, Bottom Waist Size: 32 in, Bottom Length Size: 38 in)
+XL (Top Bust Size
+ : 
+42 in, Top Length Size: 15 in, Bottom Waist Size: 34 in, Bottom Length Size: 38 in)
+XXL (Top Bust Size
+ : 
+44 in, Top Length Size: 15 in, Bottom Waist Size: 36 in, Bottom Length Size: 38 in)
+Women's Crepe Relaxed Fit with Stylish Design Palazzo
+Name
+ : 
+Women's Crepe Relaxed Fit with Stylish Design Palazzo
+Top Fabric
+ : 
+Crepe
+Bottom Fabric
+ : 
+Crepe
+Sleeve Length
+ : 
+Short Sleeves
+Net Quantity (N)
+ : 
+1
+Sizes
+ : 
+S, M, L, XL
+We presents beautiful and comfortable black &amp; white colour cobination palazzo pants With White Top made of super soft Crepe fabric which will give you very trendy and authentic look catching all the eyeballs.
+Country of Origin
+ : 
+India
 Country of Origin
  : 
 India
@@ -639,29 +637,25 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-1_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-1_img1.jpg</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-1_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-1_img2.jpg</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-1_img3.jpg</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-1_img4.jpg</t>
-        </is>
-      </c>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-1_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SWT-KUR-1766675340-2</t>
+          <t>SWT-KUR-1771586473-2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -671,7 +665,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweet India women kurta and pant set for women kurta sets</t>
+          <t>Sweet India Aishani Fashionable Dresses</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -682,7 +676,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>738</v>
+        <v>565</v>
       </c>
       <c r="H3" t="n">
         <v>50</v>
@@ -696,46 +690,55 @@
         <is>
           <t>Name
  : 
-women kurta and pant set for women kurta sets
-Kurta Fabric
- : 
-Cotton
-Bottomwear Fabric
- : 
-Cotton
+Aishani Fashionable Dresses
+Fabric
+ : 
+Crepe
 Sleeve Length
  : 
+Short Sleeves
+Pattern
+ : 
+Dyed/ Washed
+Net Quantity (N)
+ : 
+1
+Sizes
+ : 
+S, M, L, XL
+TOP &amp; BOTTOM
+Name
+ : 
+TOP &amp; BOTTOM
+Top Fabric
+ : 
+Polyester
+Bottom Fabric
+ : 
+Polyester
+Sleeve Length
+ : 
 Three-Quarter Sleeves
-Set Type
- : 
-Kurta With Dupatta
-Bottom Type
- : 
-No Bottomwear
-Pattern
- : 
-Printed
 Net Quantity (N)
  : 
-Single
+1
 Sizes
  : 
-S (Bust Size
- : 
-36 in, Shoulder Size: 14 in, Kurta Waist Size: 34 in, Kurta Length Size: 42 in, Bottom Waist Size: 26 in, Bottom Length Size: 38 in)
-M (Bust Size
- : 
-38 in, Shoulder Size: 14.5 in, Kurta Waist Size: 36 in, Kurta Length Size: 42 in, Bottom Waist Size: 28 in, Bottom Length Size: 38 in)
-L (Bust Size
- : 
-40 in, Shoulder Size: 15 in, Kurta Waist Size: 38 in, Kurta Length Size: 42 in, Bottom Waist Size: 30 in, Bottom Length Size: 38 in)
-XL (Bust Size
- : 
-42 in, Shoulder Size: 15.5 in, Kurta Waist Size: 40 in, Kurta Length Size: 42 in, Bottom Waist Size: 32 in, Bottom Length Size: 38 in)
-XXL (Bust Size
- : 
-44 in, Shoulder Size: 16 in, Kurta Waist Size: 42 in, Kurta Length Size: 42 in, Bottom Waist Size: 34 in, Bottom Length Size: 38 in)
-women kurta and pant set for women kurta sets
+S (Top Bust Size
+ : 
+36 in, Top Length Size: 22 in, Bottom Waist Size: 28 in, Bottom Length Size: 39 in)
+M (Top Bust Size
+ : 
+38 in, Top Length Size: 22 in, Bottom Waist Size: 30 in, Bottom Length Size: 39 in)
+L (Top Bust Size
+ : 
+40 in, Top Length Size: 22 in, Bottom Waist Size: 32 in, Bottom Length Size: 39 in)
+XL (Top Bust Size
+ : 
+42 in, Top Length Size: 22 in, Bottom Waist Size: 34 in, Bottom Length Size: 39 in)
+Country of Origin
+ : 
+India
 Country of Origin
  : 
 India
@@ -769,29 +772,29 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-2_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-2_img1.jpg</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-2_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-2_img2.jpg</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-2_img3.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-2_img3.jpg</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-2_img4.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-2_img4.jpg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SWT-KUR-1766675340-3</t>
+          <t>SWT-KUR-1771586473-3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -801,7 +804,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweet India Women Kurta Pant Sets Women Kurta Sets With Dupatta</t>
+          <t>Sweet India Aishani Fabulous Kurtis</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -812,7 +815,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>728</v>
+        <v>538</v>
       </c>
       <c r="H4" t="n">
         <v>50</v>
@@ -826,49 +829,57 @@
         <is>
           <t>Name
  : 
-Women Kurta Pant Sets Women Kurta Sets With Dupatta
-Kurta Fabric
- : 
-Cotton Blend
+Aishani Fabulous Kurtis
 Fabric
  : 
-Cotton Blend
-Bottomwear Fabric
- : 
-Cotton Blend
+Crepe
 Sleeve Length
  : 
-Three-Quarter Sleeves
+Short Sleeves
 Pattern
  : 
-Printed
-Set Type
- : 
-Kurta with Dupatta and Bottomwear
-Stitch Type
- : 
-Stitched
+Solid
 Net Quantity (N)
  : 
-Single
-Elevate your ethnic wardrobe with our exquisite Kurta Set with Dupatta. Crafted from a luxurious cotton blend, this ensemble ensures comfort without compromising style. The intricately designed kurta features paired harmoniously with The accompanying dupatta adds a touch of grace, completing the ensemble. Perfect for any festive occasion, our kurta set promises a blend of tradition and contemporary fashion.
+1
 Sizes
  : 
 S (Bust Size
  : 
-36 in, Shoulder Size: 14 in)
+36 in, Length Size: 18 in, Waist Size: 26 in)
 M (Bust Size
  : 
-38 in, Shoulder Size: 14 in)
+38 in, Length Size: 18 in, Waist Size: 28 in)
 L (Bust Size
  : 
-40 in, Shoulder Size: 15 in)
+40 in, Length Size: 18 in, Waist Size: 30 in)
 XL (Bust Size
  : 
-42 in, Shoulder Size: 15 in)
+42 in, Length Size: 20 in, Waist Size: 32 in)
 XXL (Bust Size
  : 
-44 in, Shoulder Size: 16 in)
+44 in, Length Size: 20 in, Waist Size: 34 in)
+Classic modern women's Tops &amp; Tunics
+Name
+ : 
+Classic modern women's Tops &amp; Tunics
+Sizes
+ : 
+S (Bust Size
+ : 
+34 in, Length Size: 15 in)
+M (Bust Size
+ : 
+36 in, Length Size: 15 in)
+L (Bust Size
+ : 
+38 in, Length Size: 16 in)
+XL (Bust Size
+ : 
+40 in, Length Size: 16 in)
+Latest fancy women's t-shirt Name
+ : 
+latest fancy Women Tshirt Fabric: Crepe  Sleeve Length: Long Sleeves Pattern: Solid Multipack: 1 Sizes: S, M, L, XL Country of Origin: India
 Country of Origin
  : 
 India
@@ -902,25 +913,29 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-3_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-3_img1.jpg</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-3_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-3_img2.jpg</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-3_img3.jpg</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-3_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-3_img4.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SWT-KUR-1766675340-4</t>
+          <t>SWT-KUR-1771586473-4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -930,7 +945,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweet India kurta sets with dupattas for women</t>
+          <t>Sweet India Comfy Elegant Women Dresses</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -941,7 +956,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>737</v>
+        <v>618</v>
       </c>
       <c r="H5" t="n">
         <v>50</v>
@@ -955,46 +970,36 @@
         <is>
           <t>Name
  : 
-kurta sets with dupattas for women
-Kurta Fabric
- : 
-Cotton Blend
-Bottomwear Fabric
- : 
-Cotton Blend
+Comfy Elegant Women Dresses
+Fabric
+ : 
+Georgette
 Sleeve Length
  : 
 Three-Quarter Sleeves
 Pattern
  : 
-Embroidered
-Set Type
- : 
-Kurta with Dupatta and Bottomwear
-Stitch Type
- : 
-Stitched
+Solid
 Net Quantity (N)
  : 
-Single
-kurta sets with dupattas for women
+1
 Sizes
  : 
 S (Bust Size
  : 
-36 in, Top Length Size: 44 in, Bottom Waist Size: 28 in, Bottom Length Size: 38 in, Shoulder Size: 14 in)
+36 in, Length Size: 42 in)
 M (Bust Size
  : 
-38 in, Top Length Size: 44 in, Bottom Waist Size: 30 in, Bottom Length Size: 38 in, Shoulder Size: 14 in)
+38 in, Length Size: 42 in)
 L (Bust Size
  : 
-40 in, Top Length Size: 44 in, Bottom Waist Size: 32 in, Bottom Length Size: 38 in, Shoulder Size: 15 in)
+40 in, Length Size: 42 in)
 XL (Bust Size
  : 
-42 in, Top Length Size: 44 in, Bottom Waist Size: 34 in, Bottom Length Size: 38 in, Shoulder Size: 15 in)
+42 in, Length Size: 42 in)
 XXL (Bust Size
  : 
-44 in, Top Length Size: 44 in, Bottom Waist Size: 36 in, Bottom Length Size: 38 in, Shoulder Size: 16 in)
+44 in, Length Size: 42 in)
 Country of Origin
  : 
 India
@@ -1028,29 +1033,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-4_img1.jpg</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-4_img2.jpg</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-4_img3.jpg</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-4_img4.jpg</t>
-        </is>
-      </c>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-4_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SWT-KUR-1766675340-5</t>
+          <t>SWT-KUR-1771586473-5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1060,7 +1053,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweet India women kurta set kurti pant sets</t>
+          <t>Sweet India Aishani Fashionable Tops</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1071,7 +1064,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>790</v>
+        <v>491</v>
       </c>
       <c r="H6" t="n">
         <v>50</v>
@@ -1085,47 +1078,33 @@
         <is>
           <t>Name
  : 
-women kurta set kurti pant sets
-Kurta Fabric
- : 
-Cotton Blend
-Bottomwear Fabric
- : 
-Cotton Blend
+Aishani Fashionable Tops
+Fabric
+ : 
+Crepe
 Sleeve Length
  : 
-Three-Quarter Sleeves
-Set Type
- : 
-Kurta With Bottomwear
-Bottom Type
- : 
-Pants
+Long Sleeves
 Pattern
  : 
-Printed
+Striped
 Net Quantity (N)
  : 
-Single
+1
 Sizes
  : 
-XXS, XS, S (Bust Size
- : 
-36 in, Shoulder Size: 14 in, Kurta Waist Size: 34 in, Kurta Length Size: 42 in, Bottom Waist Size: 28 in, Bottom Length Size: 38 in)
+S (Bust Size
+ : 
+36 in, Length Size: 38 in)
 M (Bust Size
  : 
-38 in, Shoulder Size: 14.5 in, Kurta Waist Size: 36 in, Kurta Length Size: 42 in, Bottom Waist Size: 30 in, Bottom Length Size: 38 in)
+38 in, Length Size: 38 in)
 L (Bust Size
  : 
-40 in, Shoulder Size: 15 in, Kurta Waist Size: 38 in, Kurta Length Size: 42 in, Bottom Waist Size: 32 in, Bottom Length Size: 38 in)
+40 in, Length Size: 40 in)
 XL (Bust Size
  : 
-42 in, Shoulder Size: 15.5 in, Kurta Waist Size: 40 in, Kurta Length Size: 42 in, Bottom Waist Size: 34 in, Bottom Length Size: 38 in)
-XXL (Bust Size
- : 
-44 in, Shoulder Size: 16 in, Kurta Waist Size: 42 in, Kurta Length Size: 42 in, Bottom Waist Size: 35 in, Bottom Length Size: 38 in)
-XXXL
-women kurta set kurti pant
+42 in, Length Size: 40 in)
 Country of Origin
  : 
 India
@@ -1159,29 +1138,21 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-5_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-5_img1.jpg</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-5_img2.jpg</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-5_img3.jpg</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-5_img4.jpg</t>
-        </is>
-      </c>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-5_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SWT-KUR-1766675340-6</t>
+          <t>SWT-KUR-1771586473-6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1191,7 +1162,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweet India Women Stretchable Blouse For Women</t>
+          <t>Sweet India Fancy Modern Women Dresses</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1202,7 +1173,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>524</v>
+        <v>626</v>
       </c>
       <c r="H7" t="n">
         <v>50</v>
@@ -1216,46 +1187,36 @@
         <is>
           <t>Name
  : 
-Women Stretchable Blouse For Women
+Fancy Modern Women Dresses
 Fabric
  : 
-Lycra
-Fabric
- : 
-Lycra
+Georgette
 Sleeve Length
  : 
-Short Sleeves
+Long Sleeves
 Pattern
  : 
-Embroidered
-Women Blouse Stretchable blouse
+Solid
+Net Quantity (N)
+ : 
+1
 Sizes
  : 
-28 (Bust Size
- : 
-28 in, Length Size: 15 in)
-30 (Bust Size
- : 
-30 in, Length Size: 15 in)
-32 (Bust Size
- : 
-32 in, Length Size: 15 in)
-34 (Bust Size
- : 
-34 in, Length Size: 15 in)
-36 (Bust Size
- : 
-36 in, Length Size: 15 in)
-38 (Bust Size
- : 
-38 in, Length Size: 15 in)
-40 (Bust Size
- : 
-40 in, Length Size: 15 in)
-42 (Bust Size
- : 
-42 in, Length Size: 15 in)
+S (Bust Size
+ : 
+36 in, Length Size: 48 in, Waist Size: 32 in, Hip Size: 38 in, Shoulder Size: 13 in)
+M (Bust Size
+ : 
+38 in, Length Size: 48 in, Waist Size: 34 in, Hip Size: 40 in, Shoulder Size: 14 in)
+L (Bust Size
+ : 
+40 in, Length Size: 48 in, Waist Size: 36 in, Hip Size: 42 in, Shoulder Size: 15 in)
+XL (Bust Size
+ : 
+42 in, Length Size: 50 in, Waist Size: 38 in, Hip Size: 44 in, Shoulder Size: 16 in)
+XXL (Bust Size
+ : 
+44 in, Length Size: 50 in, Waist Size: 40 in, Hip Size: 46 in, Shoulder Size: 17 in)
 Country of Origin
  : 
 India
@@ -1289,29 +1250,25 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-6_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-6_img1.jpg</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-6_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-6_img2.jpg</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-6_img3.jpg</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-6_img4.jpg</t>
-        </is>
-      </c>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-6_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SWT-KUR-1766675340-7</t>
+          <t>SWT-KUR-1771586473-7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1321,7 +1278,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweet India Women partywear kurta set for women kurti pant dupatta set</t>
+          <t>Sweet India Trendy Fashionable Women Top &amp; Bottom Sets</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1332,7 +1289,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>673</v>
+        <v>537</v>
       </c>
       <c r="H8" t="n">
         <v>50</v>
@@ -1346,46 +1303,33 @@
         <is>
           <t>Name
  : 
-Women partywear kurta set for women kurti pant dupatta set
-Kurta Fabric
- : 
-Rayon Slub
-Bottomwear Fabric
- : 
-Rayon Slub
+Trendy Fashionable Women Top &amp; Bottom Sets
+Top Fabric
+ : 
+Crepe
+Bottom Fabric
+ : 
+Crepe
 Sleeve Length
  : 
-Three-Quarter Sleeves
-Pattern
- : 
-Embroidered
-Set Type
- : 
-Kurta with Dupatta and Bottomwear
-Stitch Type
- : 
-Stitched
+Short Sleeves
 Net Quantity (N)
  : 
-Single
-Discover exquisite women kurta sets for every occasion kurti pant sets! Explore our curated collection of trendy designs, vibrant colors, and comfortable fabrics. From traditional to contemporary styles, find the perfect kurta set to elevate your ethnic wardrobe. Shop now and embrace timeless elegance with our versatile range of women kurta sets
+1
 Sizes
  : 
-S (Bust Size
- : 
-36 in, Bottom Waist Size: 28 in, Bottom Length Size: 38 in, Shoulder Size: 14 in)
-M (Bust Size
- : 
-38 in, Bottom Waist Size: 30 in, Bottom Length Size: 38 in, Shoulder Size: 15 in)
-L (Bust Size
- : 
-40 in, Bottom Waist Size: 32 in, Bottom Length Size: 38 in, Shoulder Size: 15.5 in)
-XL (Bust Size
- : 
-42 in, Bottom Waist Size: 34 in, Bottom Length Size: 38 in, Shoulder Size: 16 in)
-XXL (Bust Size
- : 
-44 in, Bottom Waist Size: 36 in, Bottom Length Size: 38 in, Shoulder Size: 16.5 in)
+S (Top Bust Size
+ : 
+36 in, Top Length Size: 14 in, Bottom Waist Size: 28 in, Bottom Length Size: 38 in)
+M (Top Bust Size
+ : 
+40 in, Top Length Size: 14 in, Bottom Waist Size: 30 in, Bottom Length Size: 38 in)
+L (Top Bust Size
+ : 
+42 in, Top Length Size: 16 in, Bottom Waist Size: 32 in, Bottom Length Size: 40 in)
+XL (Top Bust Size
+ : 
+42 in, Top Length Size: 16 in, Bottom Waist Size: 34 in, Bottom Length Size: 40 in)
 Country of Origin
  : 
 India
@@ -1419,29 +1363,21 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-7_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-7_img1.jpg</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-7_img2.jpg</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-7_img3.jpg</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-7_img4.jpg</t>
-        </is>
-      </c>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-7_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SWT-KUR-1766675340-8</t>
+          <t>SWT-KUR-1771586473-8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1451,7 +1387,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweet India Women Kurta sets for women kurta with pant kurti pant sets for women</t>
+          <t>Sweet India Classy Glamorous Women Dresses</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1462,7 +1398,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>758</v>
+        <v>641</v>
       </c>
       <c r="H9" t="n">
         <v>50</v>
@@ -1476,50 +1412,36 @@
         <is>
           <t>Name
  : 
-Women Kurta sets for women kurta with pant kurti pant sets for women
-Kurta Fabric
- : 
-Cotton
-Bottomwear Fabric
- : 
-Cotton
+Classy Glamorous Women Dresses
+Fabric
+ : 
+Georgette
 Sleeve Length
  : 
 Long Sleeves
 Pattern
  : 
-Embroidered
-Set Type
- : 
-Kurta with Dupatta and Bottomwear
-Stitch Type
- : 
-Stitched
+Solid
 Net Quantity (N)
  : 
-Single
-Women Kurta sets for women kurta with pant kurti pant sets for women
-Women Kurta sets for women kurta with pant kurti pant sets for women Women Kurta sets for women kurta with pant kurti pant sets for women
+1
 Sizes
  : 
-XS (Bust Size
- : 
-34 in, Bottom Waist Size: 28 in, Bottom Length Size: 38 in, Shoulder Size: 14 in)
 S (Bust Size
  : 
-36 in, Bottom Waist Size: 28 in, Bottom Length Size: 38 in, Shoulder Size: 14.5 in)
+36 in, Length Size: 46 in, Waist Size: 32 in, Hip Size: 38 in)
 M (Bust Size
  : 
-38 in, Bottom Waist Size: 30 in, Bottom Length Size: 38 in, Shoulder Size: 15 in)
+38 in, Length Size: 46 in, Waist Size: 34 in, Hip Size: 40 in)
 L (Bust Size
  : 
-40 in, Bottom Waist Size: 32 in, Bottom Length Size: 38 in, Shoulder Size: 15.5 in)
+40 in, Length Size: 46 in, Waist Size: 36 in, Hip Size: 42 in)
 XL (Bust Size
  : 
-42 in, Bottom Waist Size: 34 in, Bottom Length Size: 38 in, Shoulder Size: 16 in)
+42 in, Length Size: 46 in, Waist Size: 38 in, Hip Size: 44 in)
 XXL (Bust Size
  : 
-44 in, Bottom Waist Size: 34 in, Bottom Length Size: 38 in, Shoulder Size: 16.5 in)
+44 in, Length Size: 46 in, Waist Size: 40 in, Hip Size: 46 in)
 Country of Origin
  : 
 India
@@ -1553,29 +1475,25 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-8_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-8_img1.jpg</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-8_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-8_img2.jpg</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-8_img3.jpg</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-8_img4.jpg</t>
-        </is>
-      </c>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-8_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SWT-KUR-1766675340-9</t>
+          <t>SWT-KUR-1771586473-9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1585,7 +1503,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweet India Women Partywear Kurta Sets For Women Dupatta Sets Kurta With Pants Kurti With Pant Cotton Kurti with pants</t>
+          <t>Sweet India Trendy Graceful Women Dresses</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1596,7 +1514,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>790</v>
+        <v>498</v>
       </c>
       <c r="H10" t="n">
         <v>50</v>
@@ -1610,97 +1528,3878 @@
         <is>
           <t>Name
  : 
-Women Partywear Kurta Sets For Women Dupatta Sets Kurta With Pants Kurti With Pant Cotton Kurti with pants
+Trendy Graceful Women Dresses
+Sleeve Length
+ : 
+Long Sleeves
+Pattern
+ : 
+Printed
+Net Quantity (N)
+ : 
+1
+Sizes
+ : 
+S (Bust Size
+ : 
+36 in, Length Size: 38 in)
+M (Bust Size
+ : 
+38 in, Length Size: 38 in)
+L (Bust Size
+ : 
+40 in, Length Size: 38 in)
+XL (Bust Size
+ : 
+42 in, Length Size: 40 in)
+XXL (Bust Size
+ : 
+44 in, Length Size: 40 in)
+Name
+ : 
+Trendy Graceful Women Dresses
+Fabric
+ : 
+Poly Crepe
+Sleeve Length
+ : 
+Long Sleeves
+Pattern
+ : 
+Printed
+Net Quantity (N)
+ : 
+1
+Sizes
+ : 
+S, M, L, XL, XXL
+S (Bust Size
+ : 
+36 in)  M (Bust Size: 38 in)  L (Bust Size: 40 in)  XL (Bust Size: 42 in)  XXL (Bust Size: 44 in)  Daily uses kurti Country of Origin: India
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-9_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-9_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-9_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sweet India Gorgeous Woman Trendy  Tops &amp; Tunics</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>549</v>
+      </c>
+      <c r="H11" t="n">
+        <v>50</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Gorgeous Woman Trendy  Tops &amp; Tunics
+Fabric
+ : 
+Crepe
+Sleeve Length
+ : 
+Short Sleeves
+Pattern
+ : 
+Dyed/ Washed
+Net Quantity (N)
+ : 
+1
+Sizes
+ : 
+S, M, L, XL
+100% Cotton Fabric Blend Western Outfit Women Top and Skirt Set Crepe Style Pattern
+ : 
+Long Skirt For Women &amp; Girls, Type: Best worn in Daily Wear, festivals, casually in Parties, Beach Wear And Loose Fit Wrap Around Skirt with top Long flare full length skirt and top good Quality.
+These ghera skirts and top are made up of Good quality soft fabric with lining and hem of stuff fabric at edge of the flare to make the look fluppy
+1.  Skirt White Top Design for Party
+2.skirt top set for women latest design party wear
+3.long skirt top set for women latest design party wear
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-10_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-10_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-10_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-10_img4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sweet India Trendy Graceful Mens Kurtas</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>631</v>
+      </c>
+      <c r="H12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Trendy Graceful Mens Kurtas
+Fabric
+ : 
+Cotton
+Sleeve Length
+ : 
+Long Sleeves
+Pattern
+ : 
+Embellished
+Combo of
+ : 
+Single
+Sizes
+ : 
+S (Length Size
+ : 
+44 in)
+M (Length Size
+ : 
+44 in)
+L (Length Size
+ : 
+44 in)
+XL (Length Size
+ : 
+44 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-11_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-11_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-11_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-11_img4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sweet India Pretty Designer Women Dresses</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>599</v>
+      </c>
+      <c r="H13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Pretty Designer Women Dresses
+Fabric
+ : 
+Georgette
+Sleeve Length
+ : 
+Three-Quarter Sleeves
+Pattern
+ : 
+Printed
+Net Quantity (N)
+ : 
+1
+Sizes
+ : 
+S (Bust Size
+ : 
+36 in, Length Size: 50 in, Waist Size: 32 in, Hip Size: 38 in)
+M (Bust Size
+ : 
+38 in, Length Size: 50 in, Waist Size: 34 in, Hip Size: 40 in)
+XL (Bust Size
+ : 
+42 in, Length Size: 50 in, Waist Size: 40 in, Hip Size: 44 in)
+XXL (Bust Size
+ : 
+44 in, Length Size: 50 in, Waist Size: 42 in, Hip Size: 46 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-12_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-12_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sweet India Stylish  Women Dresses</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>486</v>
+      </c>
+      <c r="H14" t="n">
+        <v>50</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Stylish  Women Dresses
+Fabric
+ : 
+Crepe
+Sleeve Length
+ : 
+Long Sleeves
+Pattern
+ : 
+Printed
+Net Quantity (N)
+ : 
+1
+Sizes
+ : 
+S (Bust Size
+ : 
+36 in, Length Size: 40 in)
+M (Bust Size
+ : 
+38 in, Length Size: 40 in)
+L (Bust Size
+ : 
+40 in, Length Size: 40 in)
+XL (Bust Size
+ : 
+42 in, Length Size: 40 in)
+XXL (Bust Size
+ : 
+44 in, Length Size: 40 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-13_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-13_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-13_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sweet India Stylish Modern Women Dresses</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>605</v>
+      </c>
+      <c r="H15" t="n">
+        <v>50</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Stylish Modern Women Dresses
+Fabric
+ : 
+Georgette
+Sleeve Length
+ : 
+Long Sleeves
+Pattern
+ : 
+Solid
+Net Quantity (N)
+ : 
+1
+Sizes
+ : 
+S, L, XL, XXL
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-14_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-14_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-14_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-14_img4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sweet India Classy Elegant Women Dresses</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>630</v>
+      </c>
+      <c r="H16" t="n">
+        <v>50</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Classy Elegant Women Dresses
+Fabric
+ : 
+Cotton
+Sleeve Length
+ : 
+Long Sleeves
+Pattern
+ : 
+Printed
+Sizes
+ : 
+S (Bust Size
+ : 
+36 in)
+M (Bust Size
+ : 
+38 in)
+L (Bust Size
+ : 
+40 in)
+XL (Bust Size
+ : 
+42 in)
+XXL (Bust Size
+ : 
+44 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-15_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-15_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-15_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sweet India Fancy Men Kurtas</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>651</v>
+      </c>
+      <c r="H17" t="n">
+        <v>50</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Fancy Men Kurtas
+Fabric
+ : 
+Cotton Blend
+Sleeve Length
+ : 
+Long Sleeves
+Pattern
+ : 
+Embellished
+Combo of
+ : 
+Single
+Sizes
+ : 
+S (Length Size
+ : 
+40 in)
+M (Length Size
+ : 
+40 in)
+L (Length Size
+ : 
+42 in)
+XL (Length Size
+ : 
+42 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-16_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-16_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-16_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-16_img4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sweet India Stylish Glamorous Women Dresses</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>569</v>
+      </c>
+      <c r="H18" t="n">
+        <v>50</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Stylish Glamorous Women Dresses
+Fabric
+ : 
+Georgette
+Sleeve Length
+ : 
+Long Sleeves
+Pattern
+ : 
+Solid
+Net Quantity (N)
+ : 
+1
+Sizes
+ : 
+S (Bust Size
+ : 
+36 in, Length Size: 46 in)
+M (Bust Size
+ : 
+38 in, Length Size: 46 in)
+L (Bust Size
+ : 
+40 in, Length Size: 46 in)
+XL (Bust Size
+ : 
+42 in, Length Size: 46 in)
+XXL (Bust Size
+ : 
+44 in, Length Size: 46 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-17_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-17_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-17_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sweet India Trendy Graceful Mens Kurta</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>597</v>
+      </c>
+      <c r="H19" t="n">
+        <v>50</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Trendy Graceful Mens Kurta
+Fabric
+ : 
+Cotton
+Sleeve Length
+ : 
+Long Sleeves
+Pattern
+ : 
+Embellished
+Combo of
+ : 
+Single
+Sizes
+ : 
+S (Chest Size
+ : 
+38 in, Length Size: 50 in)
+M (Chest Size
+ : 
+40 in, Length Size: 52 in)
+L (Chest Size
+ : 
+42 in, Length Size: 52 in)
+XL (Chest Size
+ : 
+44 in, Length Size: 54 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-18_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-18_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-18_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sweet India Latest Voguish Kurtis</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>661</v>
+      </c>
+      <c r="H20" t="n">
+        <v>50</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Latest Voguish Kurtis
+Fabric
+ : 
+Georgette
+Sleeve Length
+ : 
+Three-Quarter Sleeves
+Pattern
+ : 
+Printed
+Combo of
+ : 
+Single
+Sizes
+ : 
+S (Bust Size
+ : 
+36 in, Size Length: 50 in)
+M (Bust Size
+ : 
+38 in, Size Length: 50 in)
+L (Bust Size
+ : 
+40 in, Size Length: 50 in)
+XL (Bust Size
+ : 
+42 in, Size Length: 50 in)
+XXL (Bust Size
+ : 
+44 in, Size Length: 50 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-19_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-19_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-19_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sweet India THE BEBO WESTERN WEAR TOP &amp; BOTTOM  FOR GIRLS &amp; WOMEN</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>525</v>
+      </c>
+      <c r="H21" t="n">
+        <v>50</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+THE BEBO WESTERN WEAR TOP &amp; BOTTOM  FOR GIRLS &amp; WOMEN
+Fabric
+ : 
+Poly Crepe
+Sleeve Length
+ : 
+Short Sleeves
+Pattern
+ : 
+Dyed/ Washed
+Net Quantity (N)
+ : 
+1
+Sizes
+ : 
+S (Bust Size
+ : 
+36 in, Length Size: 48 in)
+M (Bust Size
+ : 
+38 in, Length Size: 48 in)
+L (Bust Size
+ : 
+40 in, Length Size: 48 in)
+XL (Bust Size
+ : 
+42 in, Length Size: 50 in)
+XXL (Bust Size
+ : 
+44 in, Length Size: 50 in)
+THE BEBO WESTERN WEARb Fashionable Tops&amp; Bottom
+Name
+ : 
+THE BEBO WESTERN WEAR Tops&amp; Bottom
+Top Fabric
+ : 
+Crepe
+Bottom Fabric
+ : 
+Crepe
+Sleeve Length
+ : 
+Sleeveless
+Net Quantity (N)
+ : 
+1
+Sizes
+ : 
+S (Top Bust Size
+ : 
+36 in, Top Length Size: 14 in, Bottom Waist Size: 28 in, Bottom Length Size: 38 in)
+M (Top Bust Size
+ : 
+38 in, Top Length Size: 14 in, Bottom Waist Size: 30 in, Bottom Length Size: 38 in)
+L (Top Bust Size
+ : 
+40 in, Top Length Size: 14 in, Bottom Waist Size: 32 in, Bottom Length Size: 38 in)
+XL (Top Bust Size
+ : 
+42 in, Top Length Size: 15 in, Bottom Waist Size: 34 in, Bottom Length Size: 38 in)
+XXL (Top Bust Size
+ : 
+44 in, Top Length Size: 15 in, Bottom Waist Size: 36 in, Bottom Length Size: 38 in)
+Women's Crepe Relaxed Fit with Stylish Design Palazzo
+Name
+ : 
+Women's Crepe Relaxed Fit with Stylish Design Palazzo
+Top Fabric
+ : 
+Crepe
+Bottom Fabric
+ : 
+Crepe
+Sleeve Length
+ : 
+Short Sleeves
+Net Quantity (N)
+ : 
+1
+Sizes
+ : 
+S, M, L, XL
+We presents beautiful and comfortable black &amp; white colour cobination palazzo pants With White Top made of super soft Crepe fabric which will give you very trendy and authentic look catching all the eyeballs.
+Country of Origin
+ : 
+India
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-20_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-20_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-20_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Sweet India Urbane Latest Women Dresses</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>753</v>
+      </c>
+      <c r="H22" t="n">
+        <v>50</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Urbane Latest Women Dresses
 Kurta Fabric
  : 
 Cotton
 Bottomwear Fabric
  : 
 Cotton
+Kurta Color
+ : 
+Teal
+Bottomwear Color
+ : 
+Green
+Sleeve Length
+ : 
+Long Sleeves
+Sleeve Styling
+ : 
+Regular
+Neck
+ : 
+Round
+Length
+ : 
+Knee length
+Pattern
+ : 
+Embellished
+Print or Pattern Type
+ : 
+Embellished
+Bottom Type
+ : 
+Sharara
+Fit/ Shape
+ : 
+Flared
+Occasion
+ : 
+Party
+Ornamentation
+ : 
+Sequinned
+Net Quantity (N)
+ : 
+Single
+Sizes
+ : 
+S (Bust Size
+ : 
+36 in, Shoulder Size: 13 in, Kurta Length Size: 42 in, Kurta Waist Size: 34 in, Bottom Waist Size: 26 in, Bottom Length Size: 40 in)
+M (Bust Size
+ : 
+38 in, Shoulder Size: 14 in, Kurta Length Size: 42 in, Kurta Waist Size: 36 in, Bottom Waist Size: 28 in, Bottom Length Size: 40 in)
+L (Bust Size
+ : 
+40 in, Shoulder Size: 15 in, Kurta Length Size: 42 in, Kurta Waist Size: 38 in, Bottom Waist Size: 30 in, Bottom Length Size: 40 in)
+XL (Bust Size
+ : 
+42 in, Shoulder Size: 16 in, Kurta Length Size: 42 in, Kurta Waist Size: 40 in, Bottom Waist Size: 32 in, Bottom Length Size: 40 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-21_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-21_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-21_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Sweet India Trendy Graceful Girls Dresses</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>536</v>
+      </c>
+      <c r="H23" t="n">
+        <v>50</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Trendy Graceful Girls Dresses
+Top Fabric
+ : 
+Cotton
+Bottom Fabric
+ : 
+Crepe
+Sleeve Length
+ : 
+Sleeveless
+Top Pattern
+ : 
+Embellished
+Bottom Pattern
+ : 
+Applique
+Net Quantity (N)
+ : 
+Single
+Add-Ons
+ : 
+No Add Ons
+Sizes
+ : 
+3-4 Years, 4-5 Years, 5-6 Years, 6-7 Years, 7-8 Years, 8-9 Years, 9-10 Years, 10-11 Years
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-22_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-22_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-22_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sweet India Flawsome Trendy Girls Top &amp; Bottom Sets</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>554</v>
+      </c>
+      <c r="H24" t="n">
+        <v>50</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Flawsome Trendy Girls Top &amp; Bottom Sets
+Top Fabric
+ : 
+Cotton
+Bottom Fabric
+ : 
+Crepe
+Sleeve Length
+ : 
+Sleeveless
+Top Pattern
+ : 
+Embellished
+Bottom Pattern
+ : 
+Solid
+Net Quantity (N)
+ : 
+Single
+Add-Ons
+ : 
+No Add Ons
+Sizes
+ : 
+4-5 Years, 6-7 Years, 8-9 Years, 9-10 Years, 10-11 Years
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-23_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-23_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-23_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-23_img4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Sweet India Classic Men Kurtas</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>649</v>
+      </c>
+      <c r="H25" t="n">
+        <v>50</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Classic Men Kurtas
+Fabric
+ : 
+Cotton
+Sleeve Length
+ : 
+Long Sleeves
+Pattern
+ : 
+Embroidered
+Combo of
+ : 
+Single
+Sizes
+ : 
+S (Chest Size
+ : 
+38 in, Length Size: 42 in)
+M (Chest Size
+ : 
+40 in, Length Size: 42 in)
+L (Chest Size
+ : 
+42 in, Length Size: 42 in)
+XL (Chest Size
+ : 
+44 in, Length Size: 42 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-24_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-24_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-24_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-24_img4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sweet India Cotton  Women Kurti With Dupatta &amp; Bottomwear</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>624</v>
+      </c>
+      <c r="H26" t="n">
+        <v>50</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Cotton  Women Kurti With Dupatta &amp; Bottomwear
+Kurta Fabric
+ : 
+Cotton
+Bottomwear Fabric
+ : 
+Cotton
+Dupatta Fabric
+ : 
+Net
+Kurta Color
+ : 
+Aqua Blue
+Bottomwear Color
+ : 
+Aqua Blue
+Dupatta Color
+ : 
+Aqua Blue
+Sleeve Length
+ : 
+Three-Quarter Sleeves
+Sleeve Styling
+ : 
+Regular
+Length
+ : 
+Calf Length
+Neck
+ : 
+Round
+Bottom Type
+ : 
+Pants
+Pattern
+ : 
+Solid
+Print or Pattern Type
+ : 
+Solid
+Ornamentation
+ : 
+Embroidered
+Fit/ Shape
+ : 
+A-line
+Occasion
+ : 
+Party
+Net Quantity (N)
+ : 
+Single
+Sizes
+ : 
+S (Bust Size
+ : 
+36 in, Shoulder Size: 13 in, Kurta Waist Size: 34 in, Top Length Size: 40 in, Bottom Waist Size: 26 in, Bottom Length Size: 40 in, Dupatta Length Size: 1.8 in)
+M (Bust Size
+ : 
+38 in, Shoulder Size: 14 in, Kurta Waist Size: 36 in, Top Length Size: 40 in, Bottom Waist Size: 28 in, Bottom Length Size: 40 in, Dupatta Length Size: 1.8 in)
+L (Bust Size
+ : 
+40 in, Shoulder Size: 15 in, Kurta Waist Size: 38 in, Top Length Size: 40 in, Bottom Waist Size: 30 in, Bottom Length Size: 40 in, Dupatta Length Size: 1.8 in)
+XL (Bust Size
+ : 
+42 m, Shoulder Size: 16 m, Kurta Waist Size: 40 m, Top Length Size: 40 m, Bottom Waist Size: 32 m, Bottom Length Size: 40 m, Dupatta Length Size: 1.8 m)
+XXL (Bust Size
+ : 
+44 in, Shoulder Size: 17 in, Kurta Waist Size: 42 in, Top Length Size: 40 in, Bottom Waist Size: 34 in, Bottom Length Size: 40 in, Dupatta Length Size: 1.8 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-25_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-25_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-25_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sweet India Comfy Designer Women Dresses</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>624</v>
+      </c>
+      <c r="H27" t="n">
+        <v>50</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Comfy Designer Women Dresses
+Sleeve Length
+ : 
+Long Sleeves
+Pattern
+ : 
+Solid
+Sizes
+ : 
+S (Bust Size
+ : 
+36 in)
+M (Bust Size
+ : 
+38 in)
+L (Bust Size
+ : 
+40 in)
+XL (Bust Size
+ : 
+42 in)
+XXL (Bust Size
+ : 
+44 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-26_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sweet India Modern Men Kurtas</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>719</v>
+      </c>
+      <c r="H28" t="n">
+        <v>50</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Modern Men Kurtas
+Fabric
+ : 
+Cotton
+Sleeve Length
+ : 
+Long Sleeves
+Pattern
+ : 
+Embroidered
+Combo of
+ : 
+Single
+Sizes
+ : 
+S (Length Size
+ : 
+38 in)
+M (Length Size
+ : 
+38 in)
+L (Length Size
+ : 
+40 in)
+XL (Length Size
+ : 
+40 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-27_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-27_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-27_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-27_img4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sweet India Pretty Elegant Girls Top &amp; Bottom Sets</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>544</v>
+      </c>
+      <c r="H29" t="n">
+        <v>50</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Pretty Elegant Girls Top &amp; Bottom Sets
+Top Fabric
+ : 
+Cotton
+Bottom Fabric
+ : 
+Crepe
+Sleeve Length
+ : 
+Sleeveless
+Top Pattern
+ : 
+Embellished
+Bottom Pattern
+ : 
+Embellished
+Net Quantity (N)
+ : 
+Single
+Add-Ons
+ : 
+No Add Ons
+Sizes
+ : 
+3-4 Years, 4-5 Years, 5-6 Years, 6-7 Years, 7-8 Years, 8-9 Years, 9-10 Years, 10-11 Years
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-28_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-28_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-28_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-28_img4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sweet India Fancy Men Kurtas</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>644</v>
+      </c>
+      <c r="H30" t="n">
+        <v>50</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Fancy Men Kurtas
+Fabric
+ : 
+Cotton
+Sleeve Length
+ : 
+Long Sleeves
+Pattern
+ : 
+Embellished
+Combo of
+ : 
+Single
+Sizes
+ : 
+S (Chest Size
+ : 
+38 in, Length Size: 38 in)
+M (Chest Size
+ : 
+40 in, Length Size: 38 in)
+L (Chest Size
+ : 
+42 in, Length Size: 40 in)
+XL (Chest Size
+ : 
+44 in, Length Size: 40 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-29_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Sweet India Fabulous Kurti Fabrics</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>483</v>
+      </c>
+      <c r="H31" t="n">
+        <v>50</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Fabulous Kurti Fabrics
+Fabric
+ : 
+Crepe
+Pattern
+ : 
+Printed
+Net Quantity (N)
+ : 
+1
+Sizes
+ : 
+Semi Stitched (Length Size
+ : 
+4+ m)
+Un Stitched (Length Size
+ : 
+4+ m)
+Free Size (Length Size
+ : 
+4+ m)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-30_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sweet India Fashionable Men Kurtas</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>672</v>
+      </c>
+      <c r="H32" t="n">
+        <v>50</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Fashionable Men Kurtas
+Fabric
+ : 
+Cotton
+Sleeve Length
+ : 
+Long Sleeves
+Pattern
+ : 
+Embroidered
+Combo of
+ : 
+Single
+Sizes
+ : 
+S (Length Size
+ : 
+40 in)
+M (Length Size
+ : 
+40 in)
+L (Length Size
+ : 
+40 in)
+XL (Length Size
+ : 
+40 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-31_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-31_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-31_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-31_img4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sweet India Trendy Graceful Mens Mirror Kurta</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>635</v>
+      </c>
+      <c r="H33" t="n">
+        <v>50</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Trendy Graceful Mens Mirror Kurta
+Fabric
+ : 
+Cotton
+Sleeve Length
+ : 
+Long Sleeves
+Pattern
+ : 
+Embroidered
+Combo of
+ : 
+Single
+Sizes
+ : 
+S (Length Size
+ : 
+38 in)
+M (Length Size
+ : 
+38 in)
+L (Length Size
+ : 
+40 in)
+XL (Length Size
+ : 
+41 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-32_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-32_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-32_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-32_img4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sweet India Gorgeous Girls Trendy Dress</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>682</v>
+      </c>
+      <c r="H34" t="n">
+        <v>50</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Gorgeous Girls Trendy Dress
+Fabric
+ : 
+Cotton
+Sleeve Length
+ : 
+Sleeveless
+Pattern
+ : 
+Printed
+Net Quantity (N)
+ : 
+1
+Sizes
+ : 
+S (Bust Size
+ : 
+36 in, Length Size: 42 in, Waist Size: 34 in, Shoulder Size: 13 in)
+M (Bust Size
+ : 
+38 in, Length Size: 42 in, Waist Size: 36 in, Shoulder Size: 14 in)
+L (Bust Size
+ : 
+40 in, Length Size: 42 in, Waist Size: 38 in, Shoulder Size: 15 in)
+XL (Bust Size
+ : 
+42 in, Length Size: 42 in, Waist Size: 40 in, Shoulder Size: 16 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-33_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-33_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-33_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sweet India Unique Men Kurtas</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>678</v>
+      </c>
+      <c r="H35" t="n">
+        <v>50</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Unique Men Kurtas
+Fabric
+ : 
+Cotton
+Sleeve Length
+ : 
+Long Sleeves
+Pattern
+ : 
+Embroidered
+Combo of
+ : 
+Single
+Sizes
+ : 
+S (Chest Size
+ : 
+38 in, Length Size: 38 in)
+M (Chest Size
+ : 
+40 in, Length Size: 38 in)
+L (Chest Size
+ : 
+42 in, Length Size: 38 in)
+XL (Chest Size
+ : 
+44 in, Length Size: 40 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-34_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sweet India Urbane Latest kurtis</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>659</v>
+      </c>
+      <c r="H36" t="n">
+        <v>50</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Urbane Latest kurtis
+Top Fabric
+ : 
+Crepe
+Bottom Fabric
+ : 
+Crepe
+Sleeve Length
+ : 
+Long Sleeves
+Net Quantity (N)
+ : 
+1
+Sizes
+ : 
+S (Top Bust Size
+ : 
+36 in, Top Length Size: 24 in, Top Hip Size: 38 in, Bottom Waist Size: 26 in, Bottom Hip Size: 30 in, Bottom Length Size: 34 in)
+M (Top Bust Size
+ : 
+38 in, Top Length Size: 25 in, Top Hip Size: 40 in, Bottom Waist Size: 28 in, Bottom Hip Size: 32 in, Bottom Length Size: 35 in)
+L (Top Bust Size
+ : 
+40 in, Top Length Size: 26 in, Top Hip Size: 42 in, Bottom Waist Size: 30 in, Bottom Hip Size: 34 in, Bottom Length Size: 36 in)
+XL (Top Bust Size
+ : 
+42 in, Top Length Size: 27 in, Top Hip Size: 44 in, Bottom Waist Size: 32 in, Bottom Hip Size: 36 in, Bottom Length Size: 37 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-35_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-35_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-35_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-35_img4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sweet India Kashvi Refined Women Kurta Sets</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>834</v>
+      </c>
+      <c r="H37" t="n">
+        <v>50</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Kashvi Refined Women Kurta Sets
+Kurta Fabric
+ : 
+Georgette
+Bottomwear Fabric
+ : 
+Georgette
+Sleeve Length
+ : 
+Sleeveless
+Set Type
+ : 
+Kurta With Dupatta And Bottomwear
+Bottom Type
+ : 
+Sharara
+Pattern
+ : 
+Embroidered
+Net Quantity (N)
+ : 
+Single
+Sizes
+ : 
+XL (Bust Size
+ : 
+42 in, Shoulder Size: 15 in, Kurta Waist Size: 40 in, Kurta Length Size: 40 in, Bottom Waist Size: 34 in, Bottom Length Size: 36 in)
+XXL (Bust Size
+ : 
+44 in, Shoulder Size: 16 in, Kurta Waist Size: 42 in, Kurta Length Size: 40 in, Bottom Waist Size: 36 in, Bottom Length Size: 36 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-36_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-36_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Sweet India Cotton  Women Kurti With Dupatta &amp; Bottomwear</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>605</v>
+      </c>
+      <c r="H38" t="n">
+        <v>50</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Cotton  Women Kurti With Dupatta &amp; Bottomwear
+Kurta Fabric
+ : 
+Rayon Slub
+Bottomwear Fabric
+ : 
+Rayon Slub
+Dupatta Fabric
+ : 
+Rayon Slub
+Kurta Color
+ : 
+Black
+Bottomwear Color
+ : 
+Black
+Dupatta Color
+ : 
+Black
+Sleeve Length
+ : 
+Three-Quarter Sleeves
+Sleeve Styling
+ : 
+Regular
+Length
+ : 
+Calf Length
+Neck
+ : 
+V-neck
+Bottom Type
+ : 
+Pants
+Pattern
+ : 
+Printed
+Print or Pattern Type
+ : 
+Floral
+Ornamentation
+ : 
+Lace border
+Fit/ Shape
+ : 
+A-line
+Occasion
+ : 
+Festive
+Net Quantity (N)
+ : 
+Single
+Sizes
+ : 
+S (Bust Size
+ : 
+36 in, Shoulder Size: 14 in, Kurta Waist Size: 34 in, Top Length Size: 42 in, Bottom Waist Size: 28 in, Bottom Length Size: 42 in, Dupatta Length Size: 1.8 in)
+M (Bust Size
+ : 
+38 in, Shoulder Size: 15 in, Kurta Waist Size: 36 in, Top Length Size: 42 in, Bottom Waist Size: 30 in, Bottom Length Size: 42 in, Dupatta Length Size: 1.8 in)
+L (Bust Size
+ : 
+40 in, Shoulder Size: 16 in, Kurta Waist Size: 38 in, Top Length Size: 42 in, Bottom Waist Size: 32 in, Bottom Length Size: 42 in, Dupatta Length Size: 1.8 in)
+XL (Bust Size
+ : 
+42 in, Shoulder Size: 17 in, Kurta Waist Size: 40 in, Top Length Size: 42 in, Bottom Waist Size: 34 in, Bottom Length Size: 42 in, Dupatta Length Size: 1.8 in)
+XXL (Bust Size
+ : 
+44 in, Shoulder Size: 18 in, Kurta Waist Size: 42 in, Top Length Size: 42 in, Bottom Waist Size: 36 in, Bottom Length Size: 42 in, Dupatta Length Size: 1.8 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-37_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-37_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Sweet India Urbane Latest Women Kurtis</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>638</v>
+      </c>
+      <c r="H39" t="n">
+        <v>50</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Urbane Latest Women Kurtis
+Fabric
+ : 
+Georgette
 Sleeve Length
  : 
 Three-Quarter Sleeves
 Pattern
  : 
-Solid
-Set Type
- : 
-Kurta with Dupatta and Bottomwear
-Stitch Type
- : 
-Stitched
-Net Quantity (N)
+Printed
+Combo of
  : 
 Single
-Women Partywear Kurta Sets For Women Dupatta Sets Kurta With Pants Kurti With Pant Cotton Kurti with pants
 Sizes
  : 
 S (Bust Size
  : 
-36 in, Bottom Waist Size: 34 in, Bottom Length Size: 38 in, Shoulder Size: 14 in)
+36 in, Size Length: 40 in)
 M (Bust Size
  : 
-38 in, Bottom Waist Size: 36 in, Bottom Length Size: 38 in, Shoulder Size: 14.5 in)
+38 in, Size Length: 40 in)
 L (Bust Size
  : 
-40 in, Bottom Waist Size: 38 in, Bottom Length Size: 38 in, Shoulder Size: 15 in)
+40 in, Size Length: 40 in)
 XL (Bust Size
  : 
-42 in, Bottom Waist Size: 40 in, Bottom Length Size: 38 in, Shoulder Size: 15.5 in)
-XXL (Bust Size
- : 
-44 in, Bottom Waist Size: 42 in, Bottom Length Size: 38 in, Shoulder Size: 16 in)
+42 in, Size Length: 40 in)
 Country of Origin
  : 
 India
 More Information</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Care Instructions: Machine Wash</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>Fit Type: Regular Fit</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Style: Modern &amp; Trendy Design</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>kurti for women, latest design, cotton kurta, party wear</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-9_img1.jpg</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-9_img2.jpg</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-9_img3.jpg</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-9_img4.jpg</t>
-        </is>
-      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-38_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-38_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-38_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sweet India Urbane Latest kurtis</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>603</v>
+      </c>
+      <c r="H40" t="n">
+        <v>50</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Urbane Latest kurtis
+Fabric
+ : 
+Georgette
+Sleeve Length
+ : 
+Three-Quarter Sleeves
+Pattern
+ : 
+Embroidered
+Combo of
+ : 
+Single
+Sizes
+ : 
+S (Bust Size
+ : 
+36 in, Size Length: 40 in)
+M (Bust Size
+ : 
+38 in, Size Length: 40 in)
+L (Bust Size
+ : 
+40 in, Size Length: 40 in)
+XL (Bust Size
+ : 
+42 in, Size Length: 40 in)
+XXL (Bust Size
+ : 
+44 in, Size Length: 40 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-39_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-39_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-39_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-39_img4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Sweet India Gorgeous Woman Trendy Dress</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>521</v>
+      </c>
+      <c r="H41" t="n">
+        <v>50</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Gorgeous Woman Trendy Dress
+Fabric
+ : 
+Crepe
+Sleeve Length
+ : 
+Three-Quarter Sleeves
+Pattern
+ : 
+Striped
+Net Quantity (N)
+ : 
+1
+Sizes
+ : 
+S (Bust Size
+ : 
+36 in, Length Size: 39 in)
+M (Bust Size
+ : 
+38 in, Length Size: 39 in)
+L (Bust Size
+ : 
+40 in, Length Size: 40 in)
+XL (Bust Size
+ : 
+42 in, Length Size: 40 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-40_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-40_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SWT-KUR-1771586473-41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sweet India</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Sweet India Elegant Men Kurtas</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>kurta</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>668</v>
+      </c>
+      <c r="H42" t="n">
+        <v>50</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Name
+ : 
+Elegant Men Kurtas
+Fabric
+ : 
+Cotton
+Sleeve Length
+ : 
+Long Sleeves
+Pattern
+ : 
+Embellished
+Combo of
+ : 
+Single
+Sizes
+ : 
+S (Chest Size
+ : 
+38 in, Length Size: 38 in)
+M (Chest Size
+ : 
+40 in, Length Size: 38 in)
+L (Chest Size
+ : 
+42 in, Length Size: 40 in)
+XL (Chest Size
+ : 
+44 in, Length Size: 40 in)
+Country of Origin
+ : 
+India
+More Information</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Care Instructions: Machine Wash</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Fit Type: Regular Fit</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Style: Modern &amp; Trendy Design</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>kurti for women, latest design, cotton kurta, party wear</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-41_img1.jpg</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-41_img2.jpg</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771586473-41_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Final_Amazon_Upload.xlsx
+++ b/Final_Amazon_Upload.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,97 +417,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>item_sku</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>item_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>external_product_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>external_product_id_type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>feed_product_type</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>standard_price</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>update_delete</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>product_description</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>bullet_point1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>bullet_point2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>bullet_point3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>department_name</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>generic_keywords</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>main_image_url</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>other_image_url1</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>other_image_url2</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>other_image_url3</t>
         </is>
@@ -528,7 +516,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SWT-KUR-1766675340-1</t>
+          <t>SWT-KUR-1771591058-1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -639,29 +627,29 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-1_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-1_img1.jpg</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-1_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-1_img2.jpg</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-1_img3.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-1_img3.jpg</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-1_img4.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-1_img4.jpg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SWT-KUR-1766675340-2</t>
+          <t>SWT-KUR-1771591058-2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -769,29 +757,29 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-2_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-2_img1.jpg</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-2_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-2_img2.jpg</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-2_img3.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-2_img3.jpg</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-2_img4.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-2_img4.jpg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SWT-KUR-1766675340-3</t>
+          <t>SWT-KUR-1771591058-3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -902,17 +890,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-3_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-3_img1.jpg</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-3_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-3_img2.jpg</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-3_img3.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-3_img3.jpg</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
@@ -920,7 +908,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SWT-KUR-1766675340-4</t>
+          <t>SWT-KUR-1771591058-4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1028,29 +1016,29 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-4_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-4_img1.jpg</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-4_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-4_img2.jpg</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-4_img3.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-4_img3.jpg</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-4_img4.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-4_img4.jpg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SWT-KUR-1766675340-5</t>
+          <t>SWT-KUR-1771591058-5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1159,29 +1147,29 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-5_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-5_img1.jpg</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-5_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-5_img2.jpg</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-5_img3.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-5_img3.jpg</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-5_img4.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-5_img4.jpg</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SWT-KUR-1766675340-6</t>
+          <t>SWT-KUR-1771591058-6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1289,29 +1277,29 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-6_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-6_img1.jpg</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-6_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-6_img2.jpg</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-6_img3.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-6_img3.jpg</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-6_img4.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-6_img4.jpg</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SWT-KUR-1766675340-7</t>
+          <t>SWT-KUR-1771591058-7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1419,29 +1407,29 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-7_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-7_img1.jpg</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-7_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-7_img2.jpg</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-7_img3.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-7_img3.jpg</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-7_img4.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-7_img4.jpg</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SWT-KUR-1766675340-8</t>
+          <t>SWT-KUR-1771591058-8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1553,29 +1541,29 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-8_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-8_img1.jpg</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-8_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-8_img2.jpg</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-8_img3.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-8_img3.jpg</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-8_img4.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-8_img4.jpg</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SWT-KUR-1766675340-9</t>
+          <t>SWT-KUR-1771591058-9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1683,22 +1671,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-9_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-9_img1.jpg</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-9_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-9_img2.jpg</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-9_img3.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-9_img3.jpg</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1766675340-9_img4.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-9_img4.jpg</t>
         </is>
       </c>
     </row>

--- a/Final_Amazon_Upload.xlsx
+++ b/Final_Amazon_Upload.xlsx
@@ -516,7 +516,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SWT-KUR-1771591058-1</t>
+          <t>SWT-KUR-1772502831-1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -627,29 +627,29 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-1_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-1_img1.jpg</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-1_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-1_img2.jpg</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-1_img3.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-1_img3.jpg</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-1_img4.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-1_img4.jpg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SWT-KUR-1771591058-2</t>
+          <t>SWT-KUR-1772502831-2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -757,29 +757,29 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-2_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-2_img1.jpg</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-2_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-2_img2.jpg</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-2_img3.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-2_img3.jpg</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-2_img4.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-2_img4.jpg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SWT-KUR-1771591058-3</t>
+          <t>SWT-KUR-1772502831-3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -890,17 +890,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-3_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-3_img1.jpg</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-3_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-3_img2.jpg</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-3_img3.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-3_img3.jpg</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
@@ -908,7 +908,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SWT-KUR-1771591058-4</t>
+          <t>SWT-KUR-1772502831-4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1016,29 +1016,25 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-4_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-4_img1.jpg</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-4_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-4_img2.jpg</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-4_img3.jpg</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-4_img4.jpg</t>
-        </is>
-      </c>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-4_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SWT-KUR-1771591058-5</t>
+          <t>SWT-KUR-1772502831-5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1147,29 +1143,29 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-5_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-5_img1.jpg</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-5_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-5_img2.jpg</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-5_img3.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-5_img3.jpg</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-5_img4.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-5_img4.jpg</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SWT-KUR-1771591058-6</t>
+          <t>SWT-KUR-1772502831-6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1277,29 +1273,25 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-6_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-6_img1.jpg</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-6_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-6_img2.jpg</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-6_img3.jpg</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-6_img4.jpg</t>
-        </is>
-      </c>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-6_img3.jpg</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SWT-KUR-1771591058-7</t>
+          <t>SWT-KUR-1772502831-7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1407,29 +1399,29 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-7_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-7_img1.jpg</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-7_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-7_img2.jpg</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-7_img3.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-7_img3.jpg</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-7_img4.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-7_img4.jpg</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SWT-KUR-1771591058-8</t>
+          <t>SWT-KUR-1772502831-8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1541,29 +1533,29 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-8_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-8_img1.jpg</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-8_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-8_img2.jpg</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-8_img3.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-8_img3.jpg</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-8_img4.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-8_img4.jpg</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SWT-KUR-1771591058-9</t>
+          <t>SWT-KUR-1772502831-9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1671,22 +1663,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-9_img1.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-9_img1.jpg</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-9_img2.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-9_img2.jpg</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-9_img3.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-9_img3.jpg</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1771591058-9_img4.jpg</t>
+          <t>https://raw.githubusercontent.com/mademoneyai-hub/sweet-india-products/main/SWT-KUR-1772502831-9_img4.jpg</t>
         </is>
       </c>
     </row>
